--- a/airtable_json_uploader/json_files/Airtable - Baiwei Profiles.xlsx
+++ b/airtable_json_uploader/json_files/Airtable - Baiwei Profiles.xlsx
@@ -1153,26 +1153,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -1183,7 +1183,27 @@
         <v>38</v>
       </c>
       <c r="P2" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N2&amp;"" and values ""&amp;M2&amp;"" separated by character '|' and Using ""&amp;L2&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Double-Sided"", ""Dimension"": ""53mm (W) x 14mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5314-DS""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O2&amp;"", Values: ""&amp;M2&amp; "" and SKU Code: ""&amp;L2"&amp;")"),"{""Channel Configuration"": ""Double-Sided"", ""Dimension"": ""53mm (W) x 14mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5314-DS""}")</f>
         <v>{"Channel Configuration": "Double-Sided", "Dimension": "53mm (W) x 14mm (H)", "Finish": "Silver", "SKU": "TP5314-DS"}</v>
       </c>
       <c r="Q2" s="15" t="s">
@@ -1206,45 +1226,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -1252,15 +1272,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q2)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""53mm (W) x 14mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mappings"""&amp;": [{""sku"": ""TP5314-DS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q2)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""53mm (W) x 14mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mappings"""&amp;": [{""sku"": ""TP5314-DS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Double-Sided", "id": "101"}], "Dimension": [{"name": "53mm (W) x 14mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP5314-DS", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U2" s="18" t="s">
@@ -1340,26 +1360,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -1370,7 +1390,27 @@
         <v>38</v>
       </c>
       <c r="P3" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N3&amp;"" and values ""&amp;M3&amp;"" separated by character '|' and Using ""&amp;L3&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Bendable Single-Sided"", ""Dimension"": ""34.4mm (W) x 14mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP3414-SS-BEND""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O3&amp;"", Values: ""&amp;M3&amp; "" and SKU Code: ""&amp;L3"&amp;")"),"{""Channel Configuration"": ""Bendable Single-Sided"", ""Dimension"": ""34.4mm (W) x 14mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP3414-SS-BEND""}")</f>
         <v>{"Channel Configuration": "Bendable Single-Sided", "Dimension": "34.4mm (W) x 14mm (H)", "Finish": "Silver", "SKU": "TP3414-SS-BEND"}</v>
       </c>
       <c r="Q3" s="15" t="s">
@@ -1393,45 +1433,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -1439,15 +1479,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q3)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""34.4mm (W) x 14mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP3414-SS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q3)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""34.4mm (W) x 14mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP3414-SS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Bendable Single-Sided", "id": "101"}], "Dimension": [{"name": "34.4mm (W) x 14mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP3414-SS-BEND", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U3" s="18" t="s">
@@ -1527,26 +1567,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -1557,7 +1597,27 @@
         <v>38</v>
       </c>
       <c r="P4" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N4&amp;"" and values ""&amp;M4&amp;"" separated by character '|' and Using ""&amp;L4&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""51mm (W) x 13.1mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5113-DS-BEND""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O4&amp;"", Values: ""&amp;M4&amp; "" and SKU Code: ""&amp;L4"&amp;")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""51mm (W) x 13.1mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5113-DS-BEND""}")</f>
         <v>{"Channel Configuration": "Bendable Double-Sided", "Dimension": "51mm (W) x 13.1mm (H)", "Finish": "Silver", "SKU": "TP5113-DS-BEND"}</v>
       </c>
       <c r="Q4" s="15" t="s">
@@ -1580,45 +1640,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -1626,15 +1686,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q4)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""51mm (W) x 13.1mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP5113-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q4)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""51mm (W) x 13.1mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP5113-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Bendable Double-Sided", "id": "101"}], "Dimension": [{"name": "51mm (W) x 13.1mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP5113-DS-BEND", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U4" s="18" t="s">
@@ -1714,26 +1774,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -1744,7 +1804,27 @@
         <v>38</v>
       </c>
       <c r="P5" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N5&amp;"" and values ""&amp;M5&amp;"" separated by character '|' and Using ""&amp;L5&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""52.6mm (W) x 13.7mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5213-DS-BEND""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O5&amp;"", Values: ""&amp;M5&amp; "" and SKU Code: ""&amp;L5"&amp;")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""52.6mm (W) x 13.7mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5213-DS-BEND""}")</f>
         <v>{"Channel Configuration": "Bendable Double-Sided", "Dimension": "52.6mm (W) x 13.7mm (H)", "Finish": "Silver", "SKU": "TP5213-DS-BEND"}</v>
       </c>
       <c r="Q5" s="15" t="s">
@@ -1767,45 +1847,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -1813,15 +1893,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q5)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""52.6mm (W) x 13.7mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""s"&amp;"ku_mappings"": [{""sku"": ""TP5213-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q5)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""52.6mm (W) x 13.7mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""s"&amp;"ku_mappings"": [{""sku"": ""TP5213-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Bendable Double-Sided", "id": "101"}], "Dimension": [{"name": "52.6mm (W) x 13.7mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP5213-DS-BEND", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U5" s="18" t="s">
@@ -1901,26 +1981,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -1931,7 +2011,27 @@
         <v>38</v>
       </c>
       <c r="P6" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N6&amp;"" and values ""&amp;M6&amp;"" separated by character '|' and Using ""&amp;L6&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""60mm (W) x 12.9mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6013-DS-BEND""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O6&amp;"", Values: ""&amp;M6&amp; "" and SKU Code: ""&amp;L6"&amp;")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""60mm (W) x 12.9mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6013-DS-BEND""}")</f>
         <v>{"Channel Configuration": "Bendable Double-Sided", "Dimension": "60mm (W) x 12.9mm (H)", "Finish": "Silver", "SKU": "TP6013-DS-BEND"}</v>
       </c>
       <c r="Q6" s="15" t="s">
@@ -1954,45 +2054,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -2000,15 +2100,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q6)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""60mm (W) x 12.9mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP6013-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q6)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""60mm (W) x 12.9mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP6013-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Bendable Double-Sided", "id": "101"}], "Dimension": [{"name": "60mm (W) x 12.9mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP6013-DS-BEND", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U6" s="18" t="s">
@@ -2088,26 +2188,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -2118,7 +2218,27 @@
         <v>38</v>
       </c>
       <c r="P7" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N7&amp;"" and values ""&amp;M7&amp;"" separated by character '|' and Using ""&amp;L7&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""69mm (W) x 13.5mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6913-DS-BEND""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O7&amp;"", Values: ""&amp;M7&amp; "" and SKU Code: ""&amp;L7"&amp;")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""69mm (W) x 13.5mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6913-DS-BEND""}")</f>
         <v>{"Channel Configuration": "Bendable Double-Sided", "Dimension": "69mm (W) x 13.5mm (H)", "Finish": "Silver", "SKU": "TP6913-DS-BEND"}</v>
       </c>
       <c r="Q7" s="15" t="s">
@@ -2141,45 +2261,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -2187,15 +2307,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q7)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""69mm (W) x 13.5mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP6913-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q7)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""69mm (W) x 13.5mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP6913-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Bendable Double-Sided", "id": "101"}], "Dimension": [{"name": "69mm (W) x 13.5mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP6913-DS-BEND", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U7" s="18" t="s">
@@ -2275,26 +2395,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -2305,7 +2425,27 @@
         <v>38</v>
       </c>
       <c r="P8" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N8&amp;"" and values ""&amp;M8&amp;"" separated by character '|' and Using ""&amp;L8&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Single-Sided"", ""Dimension"": ""53mm (W) x 14.5mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5314-SS""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O8&amp;"", Values: ""&amp;M8&amp; "" and SKU Code: ""&amp;L8"&amp;")"),"{""Channel Configuration"": ""Single-Sided"", ""Dimension"": ""53mm (W) x 14.5mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5314-SS""}")</f>
         <v>{"Channel Configuration": "Single-Sided", "Dimension": "53mm (W) x 14.5mm (H)", "Finish": "Silver", "SKU": "TP5314-SS"}</v>
       </c>
       <c r="Q8" s="15" t="s">
@@ -2328,45 +2468,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -2374,15 +2514,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q8)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""53mm (W) x 14.5mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mappings"&amp;""": [{""sku"": ""TP5314-SS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q8)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""53mm (W) x 14.5mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mappings"&amp;""": [{""sku"": ""TP5314-SS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Single-Sided", "id": "101"}], "Dimension": [{"name": "53mm (W) x 14.5mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP5314-SS", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U8" s="18" t="s">
@@ -2462,26 +2602,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -2492,7 +2632,27 @@
         <v>38</v>
       </c>
       <c r="P9" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N9&amp;"" and values ""&amp;M9&amp;"" separated by character '|' and Using ""&amp;L9&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Single-Sided"", ""Dimension"": ""36.19mm (W) x 14mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP3614-SS""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O9&amp;"", Values: ""&amp;M9&amp; "" and SKU Code: ""&amp;L9"&amp;")"),"{""Channel Configuration"": ""Single-Sided"", ""Dimension"": ""36.19mm (W) x 14mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP3614-SS""}")</f>
         <v>{"Channel Configuration": "Single-Sided", "Dimension": "36.19mm (W) x 14mm (H)", "Finish": "Silver", "SKU": "TP3614-SS"}</v>
       </c>
       <c r="Q9" s="15" t="s">
@@ -2515,45 +2675,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -2561,15 +2721,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q9)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""36.19mm (W) x 14mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mapping"&amp;"s"": [{""sku"": ""TP3614-SS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q9)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""36.19mm (W) x 14mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mapping"&amp;"s"": [{""sku"": ""TP3614-SS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Single-Sided", "id": "101"}], "Dimension": [{"name": "36.19mm (W) x 14mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP3614-SS", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U9" s="18" t="s">
@@ -2649,26 +2809,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -2679,7 +2839,27 @@
         <v>38</v>
       </c>
       <c r="P10" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N10&amp;"" and values ""&amp;M10&amp;"" separated by character '|' and Using ""&amp;L10&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Single-Sided"", ""Dimension"": ""62mm (W) x 13mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6213-SS""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O10&amp;"", Values: ""&amp;M10&amp; "" and SKU Code: ""&amp;"&amp;"L10)"),"{""Channel Configuration"": ""Single-Sided"", ""Dimension"": ""62mm (W) x 13mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6213-SS""}")</f>
         <v>{"Channel Configuration": "Single-Sided", "Dimension": "62mm (W) x 13mm (H)", "Finish": "Silver", "SKU": "TP6213-SS"}</v>
       </c>
       <c r="Q10" s="15" t="s">
@@ -2702,45 +2882,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -2748,15 +2928,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q10)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""62mm (W) x 13mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mappings"""&amp;": [{""sku"": ""TP6213-SS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q10)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""62mm (W) x 13mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku_mappings"""&amp;": [{""sku"": ""TP6213-SS"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Single-Sided", "id": "101"}], "Dimension": [{"name": "62mm (W) x 13mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP6213-SS", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U10" s="18" t="s">
@@ -2836,26 +3016,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -2866,7 +3046,27 @@
         <v>113</v>
       </c>
       <c r="P11" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N11&amp;"" and values ""&amp;M11&amp;"" separated by character '|' and Using ""&amp;L11&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Dimension"": ""53mm (W) x 16mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5815-SS""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O11&amp;"", Values: ""&amp;M11&amp; "" and SKU Code: ""&amp;"&amp;"L11)"),"{""Dimension"": ""53mm (W) x 16mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP5815-SS""}")</f>
         <v>{"Dimension": "53mm (W) x 16mm (H)", "Finish": "Silver", "SKU": "TP5815-SS"}</v>
       </c>
       <c r="Q11" s="15" t="s">
@@ -2889,45 +3089,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -2935,15 +3135,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q11)"),"{""Options"": {""Dimension"": [{""name"": ""53mm (W) x 16mm (H)"", ""id"": ""101""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""102""}]}, ""Constraints"": {}, ""sku_mappings"": [{""sku"": ""TP5815-SS"", ""combination"": [""101"", ""102""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q11)"),"{""Options"": {""Dimension"": [{""name"": ""53mm (W) x 16mm (H)"", ""id"": ""101""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""102""}]}, ""Constraints"": {}, ""sku_mappings"": [{""sku"": ""TP5815-SS"", ""combination"": [""101"", ""102""]}]}")</f>
         <v>{"Options": {"Dimension": [{"name": "53mm (W) x 16mm (H)", "id": "101"}], "Finish": [{"name": "Silver", "id": "102"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP5815-SS", "combination": ["101", "102"]}]}</v>
       </c>
       <c r="U11" s="18" t="s">
@@ -3023,26 +3223,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -3053,7 +3253,27 @@
         <v>38</v>
       </c>
       <c r="P12" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N12&amp;"" and values ""&amp;M12&amp;"" separated by character '|' and Using ""&amp;L12&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Single-Side &amp; Dual LED"", ""Dimension"": ""116.1mm (W) x 36.5mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP11636-SS-DL""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O12&amp;"", Values: ""&amp;M12&amp; "" and SKU Code: ""&amp;"&amp;"L12)"),"{""Channel Configuration"": ""Single-Side &amp; Dual LED"", ""Dimension"": ""116.1mm (W) x 36.5mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP11636-SS-DL""}")</f>
         <v>{"Channel Configuration": "Single-Side &amp; Dual LED", "Dimension": "116.1mm (W) x 36.5mm (H)", "Finish": "Silver", "SKU": "TP11636-SS-DL"}</v>
       </c>
       <c r="Q12" s="15" t="s">
@@ -3076,45 +3296,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -3122,15 +3342,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q12)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Side &amp; Dual LED"", ""id"": ""101""}], ""Dimension"": [{""name"": ""116.1mm (W) x 36.5mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, "&amp;"""sku_mappings"": [{""sku"": ""TP11636-SS-DL"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q12)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Single-Side &amp; Dual LED"", ""id"": ""101""}], ""Dimension"": [{""name"": ""116.1mm (W) x 36.5mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, "&amp;"""sku_mappings"": [{""sku"": ""TP11636-SS-DL"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Single-Side &amp; Dual LED", "id": "101"}], "Dimension": [{"name": "116.1mm (W) x 36.5mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP11636-SS-DL", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U12" s="18" t="s">
@@ -3210,26 +3430,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -3240,7 +3460,27 @@
         <v>38</v>
       </c>
       <c r="P13" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N13&amp;"" and values ""&amp;M13&amp;"" separated by character '|' and Using ""&amp;L13&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""60mm (W) x 14.7mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6014-DS-BEND""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O13&amp;"", Values: ""&amp;M13&amp; "" and SKU Code: ""&amp;"&amp;"L13)"),"{""Channel Configuration"": ""Bendable Double-Sided"", ""Dimension"": ""60mm (W) x 14.7mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""TP6014-DS-BEND""}")</f>
         <v>{"Channel Configuration": "Bendable Double-Sided", "Dimension": "60mm (W) x 14.7mm (H)", "Finish": "Silver", "SKU": "TP6014-DS-BEND"}</v>
       </c>
       <c r="Q13" s="15" t="s">
@@ -3263,45 +3503,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -3309,15 +3549,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q13)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""60mm (W) x 14.7mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP6014-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q13)"),"{""Options"": {""Channel Configuration"": [{""name"": ""Bendable Double-Sided"", ""id"": ""101""}], ""Dimension"": [{""name"": ""60mm (W) x 14.7mm (H)"", ""id"": ""102""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""103""}]}, ""Constraints"": {}, ""sku"&amp;"_mappings"": [{""sku"": ""TP6014-DS-BEND"", ""combination"": [""101"", ""102"", ""103""]}]}")</f>
         <v>{"Options": {"Channel Configuration": [{"name": "Bendable Double-Sided", "id": "101"}], "Dimension": [{"name": "60mm (W) x 14.7mm (H)", "id": "102"}], "Finish": [{"name": "Silver", "id": "103"}]}, "Constraints": {}, "sku_mappings": [{"sku": "TP6014-DS-BEND", "combination": ["101", "102", "103"]}]}</v>
       </c>
       <c r="U13" s="18" t="s">
@@ -3397,26 +3637,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -3427,7 +3667,27 @@
         <v>113</v>
       </c>
       <c r="P14" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N14&amp;"" and values ""&amp;M14&amp;"" separated by character '|' and Using ""&amp;L14&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Dimension"": ""13.1mm (W) x 70mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""SKR1370""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O14&amp;"", Values: ""&amp;M14&amp; "" and SKU Code: ""&amp;"&amp;"L14)"),"{""Dimension"": ""13.1mm (W) x 70mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""SKR1370""}")</f>
         <v>{"Dimension": "13.1mm (W) x 70mm (H)", "Finish": "Silver", "SKU": "SKR1370"}</v>
       </c>
       <c r="Q14" s="15" t="s">
@@ -3450,45 +3710,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -3496,15 +3756,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q14)"),"{""Options"": {""Dimension"": [{""name"": ""13.1mm (W) x 70mm (H)"", ""id"": ""101""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""102""}]}, ""Constraints"": {}, ""sku_mappings"": [{""sku"": ""SKR1370"", ""combination"": [""101"", ""102""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q14)"),"{""Options"": {""Dimension"": [{""name"": ""13.1mm (W) x 70mm (H)"", ""id"": ""101""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""102""}]}, ""Constraints"": {}, ""sku_mappings"": [{""sku"": ""SKR1370"", ""combination"": [""101"", ""102""]}]}")</f>
         <v>{"Options": {"Dimension": [{"name": "13.1mm (W) x 70mm (H)", "id": "101"}], "Finish": [{"name": "Silver", "id": "102"}]}, "Constraints": {}, "sku_mappings": [{"sku": "SKR1370", "combination": ["101", "102"]}]}</v>
       </c>
       <c r="U14" s="18" t="s">
@@ -3584,26 +3844,26 @@
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
 - Light Color (Example Warm White)
-- CCT (Example 3000K)
+- Color Temperature (Example 3000K)
 - Voltage (Example 20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68)
 - Impact Strength (Example IK10)
-- Optics (Example S"&amp;"YS30°)
+- Opt"&amp;"ics (Example SYS30°)
 - Finish (Example Black finish, Silver)
 - Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
 - Dimension (Example 53mm (W) x 14mm (H))
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding l"&amp;"abels mentioned above separated by pipes ('|'). 
+1. Output ONLY the c"&amp;"orresponding labels mentioned above separated by pipes ('|'). 
 2. Do not include the values in your output.
 3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the num"&amp;"ber of values provided in the input.
+4. The number of labels in your output must exactly"&amp;" match the number of values provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-Input: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black f"&amp;"inish
+Input: 1.2W | SYM 30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V"&amp;"/24V | AC/DC | IP67 | Black
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
@@ -3614,7 +3874,27 @@
         <v>113</v>
       </c>
       <c r="P15" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N15&amp;"" and values ""&amp;M15&amp;"" separated by character '|' and Using ""&amp;L15&amp;"" and key as 'SKU', Create a JSON object"")"),"{""Dimension"": ""15.5mm (W) x 80mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""SKR1580""}")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O15&amp;"", Values: ""&amp;M15&amp; "" and SKU Code: ""&amp;"&amp;"L15)"),"{""Dimension"": ""15.5mm (W) x 80mm (H)"", ""Finish"": ""Silver"", ""SKU"": ""SKR1580""}")</f>
         <v>{"Dimension": "15.5mm (W) x 80mm (H)", "Finish": "Silver", "SKU": "SKR1580"}</v>
       </c>
       <c r="Q15" s="15" t="s">
@@ -3637,45 +3917,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -3683,15 +3963,15 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q15)"),"{""Options"": {""Dimension"": [{""name"": ""15.5mm (W) x 80mm (H)"", ""id"": ""101""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""102""}]}, ""Constraints"": {}, ""sku_mappings"": [{""sku"": ""SKR1580"", ""combination"": [""101"", ""102""]}]}")</f>
+Process the following product variant combinations and output the """"Options"""", """"Constraints"""" and """"sku_mappings"""" JSON:"", Q15)"),"{""Options"": {""Dimension"": [{""name"": ""15.5mm (W) x 80mm (H)"", ""id"": ""101""}], ""Finish"": [{""name"": ""Silver"", ""id"": ""102""}]}, ""Constraints"": {}, ""sku_mappings"": [{""sku"": ""SKR1580"", ""combination"": [""101"", ""102""]}]}")</f>
         <v>{"Options": {"Dimension": [{"name": "15.5mm (W) x 80mm (H)", "id": "101"}], "Finish": [{"name": "Silver", "id": "102"}]}, "Constraints": {}, "sku_mappings": [{"sku": "SKR1580", "combination": ["101", "102"]}]}</v>
       </c>
       <c r="U15" s="18" t="s">
